--- a/[Another tail] 예산 측정.xlsx
+++ b/[Another tail] 예산 측정.xlsx
@@ -1,26 +1,417 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\benev\OneDrive\문서\GitHub\-Game_Design-Another_Tail\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C96C6D9-8EE8-468D-B1CC-D36C6EFCB5EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="18140" yWindow="3020" windowWidth="18200" windowHeight="15190" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="팀 구조" sheetId="1" r:id="rId1"/>
+    <sheet name="인건비 예산 측정" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="92">
+  <si>
+    <t>기본 개발 직군 리스트업</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>직군</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>레벨</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>인원</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">참여 개월 수 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>비고</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>장르</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>플랫폼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>콘텐츠 규모</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>기술 스펙</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>JRPG</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>타겟  퀄리티</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>스토리비중 높음</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PC / 콘솔</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">FF7R급 3D 그래픽 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>레벨 개수</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>정적 모델 개수</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>개발 목표</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>메인 플레이타임 (시간)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">30 - 40 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>도시</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>던전</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>필드 맵</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>특수 지역</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Unreal</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3년</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>분류</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>기획</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>리드 게임 디자이너</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>시스템 디자이너</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>레벨 디자이너</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>메인 시나리오 라이터</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>서브궤스트 라이터</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>프로그래밍</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>리드 프로그래머</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>게임플레이 프로그래머</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>그래픽 / 렌더링 프로그래머</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아트</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아트 디렉터</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>콘셉트 아티스트</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3D 캐릭터 아티스트</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3D 배경 아티스트</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>애니메이터</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>VFX 아티스트</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>UI/UX 아티스트</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>사운드</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>메인 작곡가</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>추가 작곡가</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>사운드 디자이너(SFX)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>보이스 디렉터</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>QA/PM/기타</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>프로젝트 프로듀서</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>QA 리더</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>QA 테스터</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>빌드/릴리즈 매니저</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>운영/커뮤니티</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>고급</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>중급</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>초급</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>전체 기획 촉괄</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>전투/성장/UI/퀘스트 설계</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>도시/던전/필드 설계</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>메인 시나리오 구상</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>서브 퀘스트 구상</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>전체 기술 설계</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>전투/AI/스킬 구현</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>최적화/조명/셰이더</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>전체 아트 감독</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>캐릭터/배경</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>플레이어/보스/NP/몬스터</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>도시/필드/던전</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>플레이어/몬스터 애니</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>스킬/마법/폭발/UIFX</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>인게임 UI 전체</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>메인 OST</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>필드/던전 OST</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>전투/환경/인터랙션</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>성우 캐스팅/연출</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>일정/예산/PM</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>후반 품질 설계</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>후반 집중 QA</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CI/CD 릴리즈</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>출시 준비</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>등급에 따른 단가 설정</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>월 인건비(만원)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>디렉터급</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>300-350</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>400-550</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>600-800</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>800-1000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>인건비 계산 템플릿</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>인원 x 참여 개월 x 월 인건비</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -28,16 +419,47 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -45,15 +467,182 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -330,10 +919,647 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:K26"/>
+  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="11.83203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25.1640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="4.83203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="23.25" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.08203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="20.9140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="17.25" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="15" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A2" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B2" s="21" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="21" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="21" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="21" t="s">
+        <v>4</v>
+      </c>
+      <c r="F2" s="22" t="s">
+        <v>5</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A3" s="23" t="s">
+        <v>27</v>
+      </c>
+      <c r="B3" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="C3" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="D3" s="14">
+        <v>1</v>
+      </c>
+      <c r="E3" s="14">
+        <v>36</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="K3" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A4" s="24"/>
+      <c r="B4" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="D4" s="17">
+        <v>3</v>
+      </c>
+      <c r="E4" s="6">
+        <v>30</v>
+      </c>
+      <c r="F4" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="K4" s="6"/>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A5" s="24"/>
+      <c r="B5" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="D5" s="17">
+        <v>3</v>
+      </c>
+      <c r="E5" s="6">
+        <v>28</v>
+      </c>
+      <c r="F5" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="H5" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="I5" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="J5" s="5" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A6" s="24"/>
+      <c r="B6" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="D6" s="17">
+        <v>1</v>
+      </c>
+      <c r="E6" s="6">
+        <v>18</v>
+      </c>
+      <c r="F6" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="I6" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="J6" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="K6" s="5">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A7" s="25"/>
+      <c r="B7" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="D7" s="19">
+        <v>1</v>
+      </c>
+      <c r="E7" s="8">
+        <v>18</v>
+      </c>
+      <c r="F7" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="G7" s="6"/>
+      <c r="H7" s="6"/>
+      <c r="I7" s="12"/>
+      <c r="J7" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="K7" s="9">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A8" s="26" t="s">
+        <v>33</v>
+      </c>
+      <c r="B8" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="C8" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="D8" s="20">
+        <v>1</v>
+      </c>
+      <c r="E8" s="14">
+        <v>36</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="I8" s="12"/>
+      <c r="J8" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="K8" s="9">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A9" s="27"/>
+      <c r="B9" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="D9" s="17">
+        <v>4</v>
+      </c>
+      <c r="E9" s="6">
+        <v>30</v>
+      </c>
+      <c r="F9" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="I9" s="12"/>
+      <c r="J9" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="K9" s="10">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A10" s="28"/>
+      <c r="B10" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="D10" s="19">
+        <v>2</v>
+      </c>
+      <c r="E10" s="8">
+        <v>30</v>
+      </c>
+      <c r="F10" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="I10" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="J10" s="9">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A11" s="23" t="s">
+        <v>37</v>
+      </c>
+      <c r="B11" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="C11" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="D11" s="20">
+        <v>1</v>
+      </c>
+      <c r="E11" s="14">
+        <v>36</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="I11" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="J11" s="9" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A12" s="24"/>
+      <c r="B12" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="D12" s="17">
+        <v>2</v>
+      </c>
+      <c r="E12" s="6">
+        <v>25</v>
+      </c>
+      <c r="F12" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="I12" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J12" s="9" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A13" s="24"/>
+      <c r="B13" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="D13" s="17">
+        <v>2</v>
+      </c>
+      <c r="E13" s="6">
+        <v>30</v>
+      </c>
+      <c r="F13" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="H13" s="7"/>
+      <c r="I13" s="6"/>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A14" s="24"/>
+      <c r="B14" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="D14" s="17">
+        <v>3</v>
+      </c>
+      <c r="E14" s="6">
+        <v>30</v>
+      </c>
+      <c r="F14" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="H14" s="7"/>
+      <c r="I14" s="6"/>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A15" s="24"/>
+      <c r="B15" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="D15" s="17">
+        <v>2</v>
+      </c>
+      <c r="E15" s="6">
+        <v>28</v>
+      </c>
+      <c r="F15" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="H15" s="7"/>
+      <c r="I15" s="6"/>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A16" s="24"/>
+      <c r="B16" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="D16" s="17">
+        <v>1</v>
+      </c>
+      <c r="E16" s="6">
+        <v>24</v>
+      </c>
+      <c r="F16" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="I16" s="6"/>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A17" s="25"/>
+      <c r="B17" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="C17" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="D17" s="19">
+        <v>1</v>
+      </c>
+      <c r="E17" s="8">
+        <v>20</v>
+      </c>
+      <c r="F17" s="10" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A18" s="26" t="s">
+        <v>45</v>
+      </c>
+      <c r="B18" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="C18" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="D18" s="20">
+        <v>1</v>
+      </c>
+      <c r="E18" s="14">
+        <v>14</v>
+      </c>
+      <c r="F18" s="5" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A19" s="27"/>
+      <c r="B19" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="D19" s="17">
+        <v>1</v>
+      </c>
+      <c r="E19" s="6">
+        <v>7</v>
+      </c>
+      <c r="F19" s="9" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A20" s="27"/>
+      <c r="B20" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="D20" s="17">
+        <v>1</v>
+      </c>
+      <c r="E20" s="6">
+        <v>18</v>
+      </c>
+      <c r="F20" s="9" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A21" s="28"/>
+      <c r="B21" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="C21" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="D21" s="19">
+        <v>1</v>
+      </c>
+      <c r="E21" s="8">
+        <v>4</v>
+      </c>
+      <c r="F21" s="10" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A22" s="23" t="s">
+        <v>50</v>
+      </c>
+      <c r="B22" s="14" t="s">
+        <v>51</v>
+      </c>
+      <c r="C22" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="D22" s="20">
+        <v>1</v>
+      </c>
+      <c r="E22" s="14">
+        <v>36</v>
+      </c>
+      <c r="F22" s="5" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A23" s="24"/>
+      <c r="B23" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="C23" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="D23" s="17">
+        <v>1</v>
+      </c>
+      <c r="E23" s="6">
+        <v>18</v>
+      </c>
+      <c r="F23" s="9" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A24" s="24"/>
+      <c r="B24" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="C24" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="D24" s="17">
+        <v>4</v>
+      </c>
+      <c r="E24" s="6">
+        <v>12</v>
+      </c>
+      <c r="F24" s="9" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A25" s="24"/>
+      <c r="B25" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C25" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="D25" s="17">
+        <v>1</v>
+      </c>
+      <c r="E25" s="6">
+        <v>24</v>
+      </c>
+      <c r="F25" s="9" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A26" s="25"/>
+      <c r="B26" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="C26" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="D26" s="19">
+        <v>1</v>
+      </c>
+      <c r="E26" s="8">
+        <v>6</v>
+      </c>
+      <c r="F26" s="10" t="s">
+        <v>82</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D90419A6-6419-4C59-83BA-ADE2E060AC43}">
+  <dimension ref="A1:E6"/>
+  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="8.4140625" customWidth="1"/>
+    <col min="2" max="2" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.75" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="26.33203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A1" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A2" s="26" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="29" t="s">
+        <v>84</v>
+      </c>
+      <c r="D2" s="30" t="s">
+        <v>90</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A3" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A4" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A5" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A6" s="18" t="s">
+        <v>85</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>89</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/[Another tail] 예산 측정.xlsx
+++ b/[Another tail] 예산 측정.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\benev\OneDrive\문서\GitHub\-Game_Design-Another_Tail\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ARK\Documents\GitHub\Game_Design-Another_Tail\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C96C6D9-8EE8-468D-B1CC-D36C6EFCB5EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47051F70-7640-4AF8-A6B7-869F0F7EDB8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="18140" yWindow="3020" windowWidth="18200" windowHeight="15190" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4905" yWindow="1455" windowWidth="20865" windowHeight="12435" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="팀 구조" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="125">
   <si>
     <t>기본 개발 직군 리스트업</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -95,10 +95,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">FF7R급 3D 그래픽 </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>레벨 개수</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -404,6 +400,142 @@
   </si>
   <si>
     <t>인원 x 참여 개월 x 월 인건비</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>FF7R급 연출</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>전략 요소</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>필드/탐험</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>전투/스킬/보스전</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>메인 컷신/주요 도시</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>NPC/몬스터</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>UI/사운드</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>중급 3D</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AAA연출</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>주요 모델 상위 퀄리티</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>리깅/애니 재사용</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>최고 퀄리티 유지</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>콘텐츠 등급화</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>콘텐츠</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>등급</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>핵심 던전</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>보스 스테이지</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>중간 던전</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>주요 필드</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>통로형 지역</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>C</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>B</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>필드 이동/탐험은 최적화와 스타일리쉬함에 집중(리소스절약)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>요약</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>전투 진입 혹은 이벤트 컷신에서 카메라 워킹과 이펙트 비용을 투자하여 시각적 만족감을 주는 '선택과 집중'전략</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>시네마틱 연출가</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>언리얼 시퀸스 작업</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>UI/시스템 프로그래머</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>UI연출/ 최적화</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>초급/중급</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1+2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2+1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>외주</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -459,7 +591,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="15">
     <border>
       <left/>
       <right/>
@@ -584,11 +716,52 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -599,8 +772,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
@@ -614,9 +786,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
@@ -640,6 +812,29 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -920,43 +1115,44 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K26"/>
-  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
+  <dimension ref="A1:O30"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11.83203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="25.1640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="4.83203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25.125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.75" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="12.5" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="23.25" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.08203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="20.9140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="20.875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="17.25" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="15" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="19.375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="21.375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="B2" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="B2" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="21" t="s">
+      <c r="C2" s="20" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="21" t="s">
+      <c r="D2" s="20" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="21" t="s">
+      <c r="E2" s="20" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="22" t="s">
+      <c r="F2" s="21" t="s">
         <v>5</v>
       </c>
       <c r="I2" s="4" t="s">
@@ -966,51 +1162,51 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A3" s="23" t="s">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A3" s="22" t="s">
+        <v>26</v>
+      </c>
+      <c r="B3" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="B3" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="C3" s="14" t="s">
-        <v>56</v>
-      </c>
-      <c r="D3" s="14">
+      <c r="C3" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="D3" s="13">
         <v>1</v>
       </c>
-      <c r="E3" s="14">
+      <c r="E3" s="13">
         <v>36</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I3" s="4" t="s">
         <v>11</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>14</v>
+        <v>91</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A4" s="24"/>
-      <c r="B4" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="D4" s="17">
-        <v>3</v>
-      </c>
-      <c r="E4" s="6">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A4" s="23"/>
+      <c r="B4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C4" t="s">
+        <v>121</v>
+      </c>
+      <c r="D4" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="E4">
         <v>30</v>
       </c>
-      <c r="F4" s="9" t="s">
-        <v>60</v>
+      <c r="F4" s="8" t="s">
+        <v>59</v>
       </c>
       <c r="I4" s="4" t="s">
         <v>7</v>
@@ -1018,476 +1214,619 @@
       <c r="J4" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="K4" s="6"/>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A5" s="24"/>
-      <c r="B5" s="6" t="s">
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A5" s="23"/>
+      <c r="B5" t="s">
+        <v>29</v>
+      </c>
+      <c r="C5" t="s">
+        <v>121</v>
+      </c>
+      <c r="D5" s="16" t="s">
+        <v>123</v>
+      </c>
+      <c r="E5">
+        <v>28</v>
+      </c>
+      <c r="F5" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="H5" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="I5" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="J5" s="5" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A6" s="23"/>
+      <c r="B6" t="s">
         <v>30</v>
       </c>
-      <c r="C5" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="D5" s="17">
-        <v>3</v>
-      </c>
-      <c r="E5" s="6">
-        <v>28</v>
-      </c>
-      <c r="F5" s="9" t="s">
+      <c r="C6" t="s">
+        <v>56</v>
+      </c>
+      <c r="D6" s="16">
+        <v>1</v>
+      </c>
+      <c r="E6">
+        <v>18</v>
+      </c>
+      <c r="F6" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="H5" s="13" t="s">
-        <v>8</v>
-      </c>
-      <c r="I5" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="J5" s="5" t="s">
+      <c r="I6" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="J6" s="14" t="s">
         <v>19</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A6" s="24"/>
-      <c r="B6" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="D6" s="17">
-        <v>1</v>
-      </c>
-      <c r="E6" s="6">
-        <v>18</v>
-      </c>
-      <c r="F6" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="I6" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="J6" s="15" t="s">
-        <v>20</v>
       </c>
       <c r="K6" s="5">
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A7" s="25"/>
-      <c r="B7" s="8" t="s">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A7" s="24"/>
+      <c r="B7" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="D7" s="18">
+        <v>1</v>
+      </c>
+      <c r="E7" s="7">
+        <v>18</v>
+      </c>
+      <c r="F7" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="I7" s="11"/>
+      <c r="J7" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="K7" s="8">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A8" s="25" t="s">
         <v>32</v>
       </c>
-      <c r="C7" s="8" t="s">
+      <c r="B8" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="C8" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="D8" s="19">
+        <v>1</v>
+      </c>
+      <c r="E8" s="13">
+        <v>36</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="I8" s="11"/>
+      <c r="J8" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="K8" s="8">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A9" s="26"/>
+      <c r="B9" t="s">
+        <v>34</v>
+      </c>
+      <c r="C9" t="s">
+        <v>56</v>
+      </c>
+      <c r="D9" s="16">
+        <v>2</v>
+      </c>
+      <c r="E9">
+        <v>30</v>
+      </c>
+      <c r="F9" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="I9" s="11"/>
+      <c r="J9" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="K9" s="9">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A10" s="26"/>
+      <c r="B10" s="33" t="s">
+        <v>35</v>
+      </c>
+      <c r="C10" s="33" t="s">
+        <v>55</v>
+      </c>
+      <c r="D10" s="34">
+        <v>1</v>
+      </c>
+      <c r="E10" s="33">
+        <v>30</v>
+      </c>
+      <c r="F10" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="I10" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="J10" s="8">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A11" s="27"/>
+      <c r="B11" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="D11" s="18">
+        <v>1</v>
+      </c>
+      <c r="E11" s="7">
+        <v>30</v>
+      </c>
+      <c r="F11" s="9" t="s">
+        <v>120</v>
+      </c>
+      <c r="I11" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="J11" s="8" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A12" s="22" t="s">
+        <v>36</v>
+      </c>
+      <c r="B12" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="C12" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="D12" s="19">
+        <v>1</v>
+      </c>
+      <c r="E12" s="13">
+        <v>36</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="I12" s="42" t="s">
+        <v>16</v>
+      </c>
+      <c r="J12" s="9" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A13" s="23"/>
+      <c r="B13" t="s">
+        <v>38</v>
+      </c>
+      <c r="C13" t="s">
+        <v>56</v>
+      </c>
+      <c r="D13" s="16">
+        <v>2</v>
+      </c>
+      <c r="E13">
+        <v>25</v>
+      </c>
+      <c r="F13" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="H13" s="6"/>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A14" s="23"/>
+      <c r="B14" t="s">
+        <v>39</v>
+      </c>
+      <c r="C14" t="s">
+        <v>56</v>
+      </c>
+      <c r="D14" s="16">
+        <v>2</v>
+      </c>
+      <c r="E14">
+        <v>30</v>
+      </c>
+      <c r="F14" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="H14" s="6"/>
+      <c r="I14" s="31" t="s">
+        <v>92</v>
+      </c>
+      <c r="J14" s="30" t="s">
+        <v>93</v>
+      </c>
+      <c r="K14" s="5" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A15" s="23"/>
+      <c r="B15" t="s">
+        <v>40</v>
+      </c>
+      <c r="C15" t="s">
+        <v>121</v>
+      </c>
+      <c r="D15" s="16" t="s">
+        <v>123</v>
+      </c>
+      <c r="E15">
+        <v>30</v>
+      </c>
+      <c r="F15" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="H15" s="6"/>
+      <c r="J15" s="15" t="s">
+        <v>94</v>
+      </c>
+      <c r="K15" s="8" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A16" s="23"/>
+      <c r="B16" t="s">
+        <v>41</v>
+      </c>
+      <c r="C16" t="s">
+        <v>56</v>
+      </c>
+      <c r="D16" s="16">
+        <v>2</v>
+      </c>
+      <c r="E16">
+        <v>28</v>
+      </c>
+      <c r="F16" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="J16" s="15" t="s">
+        <v>95</v>
+      </c>
+      <c r="K16" s="8" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A17" s="23"/>
+      <c r="B17" t="s">
+        <v>117</v>
+      </c>
+      <c r="C17" t="s">
+        <v>56</v>
+      </c>
+      <c r="D17" s="16">
+        <v>1</v>
+      </c>
+      <c r="E17">
+        <v>24</v>
+      </c>
+      <c r="F17" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="J17" s="15" t="s">
+        <v>96</v>
+      </c>
+      <c r="K17" s="8" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A18" s="23"/>
+      <c r="B18" t="s">
+        <v>42</v>
+      </c>
+      <c r="C18" t="s">
+        <v>56</v>
+      </c>
+      <c r="D18" s="16">
+        <v>2</v>
+      </c>
+      <c r="E18">
+        <v>24</v>
+      </c>
+      <c r="F18" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="J18" s="15" t="s">
+        <v>97</v>
+      </c>
+      <c r="K18" s="8" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A19" s="24"/>
+      <c r="B19" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="D19" s="18">
+        <v>1</v>
+      </c>
+      <c r="E19" s="7">
+        <v>20</v>
+      </c>
+      <c r="F19" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="H19" s="37" t="s">
+        <v>115</v>
+      </c>
+      <c r="I19" s="38" t="s">
+        <v>114</v>
+      </c>
+      <c r="J19" s="40"/>
+      <c r="K19" s="13"/>
+      <c r="L19" s="13"/>
+      <c r="M19" s="13"/>
+      <c r="N19" s="13"/>
+      <c r="O19" s="5"/>
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A20" s="22" t="s">
+        <v>49</v>
+      </c>
+      <c r="B20" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="C20" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="D20" s="19">
+        <v>1</v>
+      </c>
+      <c r="E20" s="13">
+        <v>36</v>
+      </c>
+      <c r="F20" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="I20" s="39" t="s">
+        <v>116</v>
+      </c>
+      <c r="J20" s="41"/>
+      <c r="K20" s="7"/>
+      <c r="L20" s="7"/>
+      <c r="M20" s="7"/>
+      <c r="N20" s="7"/>
+      <c r="O20" s="9"/>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A21" s="23"/>
+      <c r="B21" t="s">
+        <v>51</v>
+      </c>
+      <c r="C21" t="s">
+        <v>56</v>
+      </c>
+      <c r="D21" s="16">
+        <v>1</v>
+      </c>
+      <c r="E21">
+        <v>18</v>
+      </c>
+      <c r="F21" s="8" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A22" s="23"/>
+      <c r="B22" t="s">
+        <v>53</v>
+      </c>
+      <c r="C22" t="s">
+        <v>56</v>
+      </c>
+      <c r="D22" s="16">
+        <v>1</v>
+      </c>
+      <c r="E22">
+        <v>24</v>
+      </c>
+      <c r="F22" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="I22" t="s">
+        <v>103</v>
+      </c>
+      <c r="J22" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="K22" s="32" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A23" s="24"/>
+      <c r="B23" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="C23" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="D7" s="19">
+      <c r="D23" s="18">
         <v>1</v>
       </c>
-      <c r="E7" s="8">
-        <v>18</v>
-      </c>
-      <c r="F7" s="10" t="s">
-        <v>63</v>
-      </c>
-      <c r="G7" s="6"/>
-      <c r="H7" s="6"/>
-      <c r="I7" s="12"/>
-      <c r="J7" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="K7" s="9">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A8" s="26" t="s">
-        <v>33</v>
-      </c>
-      <c r="B8" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="C8" s="14" t="s">
-        <v>56</v>
-      </c>
-      <c r="D8" s="20">
-        <v>1</v>
-      </c>
-      <c r="E8" s="14">
-        <v>36</v>
-      </c>
-      <c r="F8" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="I8" s="12"/>
-      <c r="J8" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="K8" s="9">
+      <c r="E23" s="7">
         <v>6</v>
       </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A9" s="27"/>
-      <c r="B9" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="C9" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="D9" s="17">
-        <v>4</v>
-      </c>
-      <c r="E9" s="6">
-        <v>30</v>
-      </c>
-      <c r="F9" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="I9" s="12"/>
-      <c r="J9" s="15" t="s">
-        <v>23</v>
-      </c>
-      <c r="K9" s="10">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A10" s="28"/>
-      <c r="B10" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="C10" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="D10" s="19">
-        <v>2</v>
-      </c>
-      <c r="E10" s="8">
-        <v>30</v>
-      </c>
-      <c r="F10" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="I10" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="J10" s="9">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A11" s="23" t="s">
-        <v>37</v>
-      </c>
-      <c r="B11" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="C11" s="14" t="s">
-        <v>56</v>
-      </c>
-      <c r="D11" s="20">
-        <v>1</v>
-      </c>
-      <c r="E11" s="14">
-        <v>36</v>
-      </c>
-      <c r="F11" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="I11" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="J11" s="9" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A12" s="24"/>
-      <c r="B12" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="C12" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="D12" s="17">
-        <v>2</v>
-      </c>
-      <c r="E12" s="6">
-        <v>25</v>
-      </c>
-      <c r="F12" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="I12" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J12" s="9" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A13" s="24"/>
-      <c r="B13" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="C13" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="D13" s="17">
-        <v>2</v>
-      </c>
-      <c r="E13" s="6">
-        <v>30</v>
-      </c>
-      <c r="F13" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="H13" s="7"/>
-      <c r="I13" s="6"/>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A14" s="24"/>
-      <c r="B14" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="C14" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="D14" s="17">
-        <v>3</v>
-      </c>
-      <c r="E14" s="6">
-        <v>30</v>
-      </c>
-      <c r="F14" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="H14" s="7"/>
-      <c r="I14" s="6"/>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A15" s="24"/>
-      <c r="B15" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="C15" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="D15" s="17">
-        <v>2</v>
-      </c>
-      <c r="E15" s="6">
-        <v>28</v>
-      </c>
-      <c r="F15" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="H15" s="7"/>
-      <c r="I15" s="6"/>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A16" s="24"/>
-      <c r="B16" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="C16" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="D16" s="17">
-        <v>1</v>
-      </c>
-      <c r="E16" s="6">
-        <v>24</v>
-      </c>
-      <c r="F16" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="I16" s="6"/>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A17" s="25"/>
-      <c r="B17" s="8" t="s">
+      <c r="F23" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="J23" s="30" t="s">
+        <v>19</v>
+      </c>
+      <c r="K23" s="5" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="J24" s="15" t="s">
+        <v>106</v>
+      </c>
+      <c r="K24" s="8" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>124</v>
+      </c>
+      <c r="J25" s="15" t="s">
+        <v>107</v>
+      </c>
+      <c r="K25" s="8" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A26" s="25" t="s">
         <v>44</v>
       </c>
-      <c r="C17" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="D17" s="19">
-        <v>1</v>
-      </c>
-      <c r="E17" s="8">
-        <v>20</v>
-      </c>
-      <c r="F17" s="10" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A18" s="26" t="s">
+      <c r="B26" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="B18" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="C18" s="14" t="s">
-        <v>56</v>
-      </c>
-      <c r="D18" s="20">
-        <v>1</v>
-      </c>
-      <c r="E18" s="14">
-        <v>14</v>
-      </c>
-      <c r="F18" s="5" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A19" s="27"/>
-      <c r="B19" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="C19" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="D19" s="17">
-        <v>1</v>
-      </c>
-      <c r="E19" s="6">
-        <v>7</v>
-      </c>
-      <c r="F19" s="9" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A20" s="27"/>
-      <c r="B20" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="C20" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="D20" s="17">
-        <v>1</v>
-      </c>
-      <c r="E20" s="6">
-        <v>18</v>
-      </c>
-      <c r="F20" s="9" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A21" s="28"/>
-      <c r="B21" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="C21" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="D21" s="19">
-        <v>1</v>
-      </c>
-      <c r="E21" s="8">
-        <v>4</v>
-      </c>
-      <c r="F21" s="10" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A22" s="23" t="s">
-        <v>50</v>
-      </c>
-      <c r="B22" s="14" t="s">
-        <v>51</v>
-      </c>
-      <c r="C22" s="14" t="s">
-        <v>56</v>
-      </c>
-      <c r="D22" s="20">
-        <v>1</v>
-      </c>
-      <c r="E22" s="14">
-        <v>36</v>
-      </c>
-      <c r="F22" s="5" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A23" s="24"/>
-      <c r="B23" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="C23" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="D23" s="17">
-        <v>1</v>
-      </c>
-      <c r="E23" s="6">
-        <v>18</v>
-      </c>
-      <c r="F23" s="9" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A24" s="24"/>
-      <c r="B24" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="C24" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="D24" s="17">
-        <v>4</v>
-      </c>
-      <c r="E24" s="6">
-        <v>12</v>
-      </c>
-      <c r="F24" s="9" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A25" s="24"/>
-      <c r="B25" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="C25" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="D25" s="17">
-        <v>1</v>
-      </c>
-      <c r="E25" s="6">
-        <v>24</v>
-      </c>
-      <c r="F25" s="9" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A26" s="25"/>
-      <c r="B26" s="8" t="s">
+      <c r="C26" s="13" t="s">
         <v>55</v>
-      </c>
-      <c r="C26" s="8" t="s">
-        <v>58</v>
       </c>
       <c r="D26" s="19">
         <v>1</v>
       </c>
-      <c r="E26" s="8">
-        <v>6</v>
-      </c>
-      <c r="F26" s="10" t="s">
-        <v>82</v>
+      <c r="E26" s="13">
+        <v>14</v>
+      </c>
+      <c r="F26" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="J26" s="15" t="s">
+        <v>108</v>
+      </c>
+      <c r="K26" s="8" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A27" s="26"/>
+      <c r="B27" t="s">
+        <v>46</v>
+      </c>
+      <c r="C27" t="s">
+        <v>56</v>
+      </c>
+      <c r="D27" s="16">
+        <v>1</v>
+      </c>
+      <c r="E27">
+        <v>7</v>
+      </c>
+      <c r="F27" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="J27" s="15" t="s">
+        <v>109</v>
+      </c>
+      <c r="K27" s="8" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A28" s="26"/>
+      <c r="B28" t="s">
+        <v>47</v>
+      </c>
+      <c r="C28" t="s">
+        <v>56</v>
+      </c>
+      <c r="D28" s="16">
+        <v>1</v>
+      </c>
+      <c r="E28">
+        <v>18</v>
+      </c>
+      <c r="F28" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="J28" s="15" t="s">
+        <v>110</v>
+      </c>
+      <c r="K28" s="8" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A29" s="27"/>
+      <c r="B29" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="C29" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="D29" s="18">
+        <v>1</v>
+      </c>
+      <c r="E29" s="7">
+        <v>4</v>
+      </c>
+      <c r="F29" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="J29" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="K29" s="9" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A30" s="35" t="s">
+        <v>49</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D30" s="36">
+        <v>4</v>
+      </c>
+      <c r="E30" s="2">
+        <v>12</v>
+      </c>
+      <c r="F30" s="3" t="s">
+        <v>79</v>
       </c>
     </row>
   </sheetData>
@@ -1499,63 +1838,63 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D90419A6-6419-4C59-83BA-ADE2E060AC43}">
   <dimension ref="A1:E6"/>
-  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.4140625" customWidth="1"/>
-    <col min="2" max="2" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.375" customWidth="1"/>
+    <col min="2" max="2" width="14.375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="17.75" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="26.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="26.375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" s="25" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="28" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A2" s="26" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" s="29" t="s">
+      <c r="D2" s="29" t="s">
+        <v>89</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="15" t="s">
+        <v>57</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" s="17" t="s">
         <v>84</v>
       </c>
-      <c r="D2" s="30" t="s">
-        <v>90</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A3" s="16" t="s">
-        <v>58</v>
-      </c>
-      <c r="B3" s="9" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A4" s="16" t="s">
-        <v>57</v>
-      </c>
-      <c r="B4" s="9" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A5" s="16" t="s">
-        <v>56</v>
-      </c>
-      <c r="B5" s="9" t="s">
+      <c r="B6" s="9" t="s">
         <v>88</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A6" s="18" t="s">
-        <v>85</v>
-      </c>
-      <c r="B6" s="10" t="s">
-        <v>89</v>
       </c>
     </row>
   </sheetData>

--- a/[Another tail] 예산 측정.xlsx
+++ b/[Another tail] 예산 측정.xlsx
@@ -8,13 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ARK\Documents\GitHub\Game_Design-Another_Tail\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47051F70-7640-4AF8-A6B7-869F0F7EDB8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{853CEA76-FAC1-41FF-8C5A-45C5DB5116B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4905" yWindow="1455" windowWidth="20865" windowHeight="12435" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2415" yWindow="405" windowWidth="16350" windowHeight="12435" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="팀 구조" sheetId="1" r:id="rId1"/>
-    <sheet name="인건비 예산 측정" sheetId="2" r:id="rId2"/>
+    <sheet name="예산 측정" sheetId="3" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="358" uniqueCount="212">
   <si>
     <t>기본 개발 직군 리스트업</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -367,42 +367,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>등급에 따른 단가 설정</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>월 인건비(만원)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>디렉터급</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>300-350</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>400-550</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>600-800</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>800-1000</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>인건비 계산 템플릿</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>인원 x 참여 개월 x 월 인건비</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>FF7R급 연출</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -536,6 +504,386 @@
   </si>
   <si>
     <t>외주</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3200 ~ 4400</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>초급(1~4년차)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>중급(5~9)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4800~ 6200</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>고급(10년차이상)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>7000~7200</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>연봉(만원)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>월급(만원)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>인건비 합계(만원)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>프로그래머</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>QA</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>인건비 합계(억원)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>운영</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>장비/SW 구매</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>회식비/워크샵비</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>소프트웨어 라이선스</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>인건비 단가표</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>외주 단가표</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BGM</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>메인 테마(보컬)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>전투/이벤트(고퀄리티)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>필드/던전(중간 퀄리티)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>효과음</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>s급 성우</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A급 성우</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>성우</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SFX</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>구분</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>단위</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>평균 단가(만원)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1곡</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10개</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1시간</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>40~60</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>150~250</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>300~500</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>800~1200</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>유명 보컬 섭외 및 오케스트라 세션포함</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>보스전, 핵심 컷신용 트랙</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>일반적인 루프 BGM</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>스킬, 타격,UI 환경음 등</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>팬덤이 두터운 유명 성우</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>일반적인 프로 성우</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>단가</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>제작 수</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>12(개월)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>스튜디오</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>인원/수량</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>기간(개월/회)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>33명</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>36개월</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>총 금액(억원)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>부서 운영비(워크샵 포함)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1식</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4회</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>단가(만원)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1회</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>특수 플러그인, 에셋 구독</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>고가 에셋 구매</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>FGT 및 외주 추가비</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>합계</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>총(만원)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Risk 예비비</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>수량/기간</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>총 개발비 5%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>물가/환율 변동, 긴급 이슈 대응 및 SW라이선스 인상분 대비</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>총액(억원)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>예산 측정</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>예비</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>8~12</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>80~120</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>총 예산 측정(억원)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>다음 페이지 : 예산 측정</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1차 피드백</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PM과 어드바이저가 빠졌다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>게임 디자이너 PM</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>프로그래머 PM</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>네트워크 관리</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아트 디렉터 PM</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>툴/파이프라인 프로그래머</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>중급/상급</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>오늘날 아트 쪽이 많이 침체기다. 인원수 조정하라</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>피드백</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>반영 결과</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>기획PM 2명, 프로그래머 PM 2명, 아트 PM 1명 추가</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아트 인원 13명에서 11명 감소,</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>네트워크/백엔드 프로그래머</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3+3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AI/전투 프로그래머</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>객체의 AI 및 전투 구현</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>게임 기본 골자 구현 및 수정</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>프로그래머 인원수 21명으로 조정</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>기획 인원수 19명으로 조정</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -543,7 +891,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -558,8 +906,68 @@
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="18"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="20"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -590,8 +998,26 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="15">
+  <borders count="16">
     <border>
       <left/>
       <right/>
@@ -757,11 +1183,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="97">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -810,17 +1247,11 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -828,12 +1259,116 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="13" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1115,14 +1650,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O30"/>
+  <dimension ref="A1:O35"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="25.125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.75" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.875" customWidth="1"/>
+    <col min="4" max="5" width="21.5" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="23.25" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="11.125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="20.875" bestFit="1" customWidth="1"/>
@@ -1131,10 +1665,15 @@
     <col min="11" max="11" width="21.375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B1" t="s">
+    <row r="1" spans="1:11" ht="26.25" x14ac:dyDescent="0.45">
+      <c r="A1" s="38"/>
+      <c r="B1" s="38"/>
+      <c r="C1" s="38" t="s">
         <v>0</v>
       </c>
+      <c r="D1" s="38"/>
+      <c r="E1" s="38"/>
+      <c r="F1" s="38"/>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
@@ -1185,7 +1724,7 @@
         <v>11</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>12</v>
@@ -1197,10 +1736,10 @@
         <v>28</v>
       </c>
       <c r="C4" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="D4" s="16" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="E4">
         <v>30</v>
@@ -1221,10 +1760,10 @@
         <v>29</v>
       </c>
       <c r="C5" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="D5" s="16" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="E5">
         <v>28</v>
@@ -1348,16 +1887,16 @@
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" s="26"/>
-      <c r="B10" s="33" t="s">
+      <c r="B10" t="s">
         <v>35</v>
       </c>
-      <c r="C10" s="33" t="s">
+      <c r="C10" t="s">
         <v>55</v>
       </c>
-      <c r="D10" s="34">
+      <c r="D10" s="16">
         <v>1</v>
       </c>
-      <c r="E10" s="33">
+      <c r="E10">
         <v>30</v>
       </c>
       <c r="F10" s="8" t="s">
@@ -1373,7 +1912,7 @@
     <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" s="27"/>
       <c r="B11" s="7" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="C11" s="7" t="s">
         <v>56</v>
@@ -1385,7 +1924,7 @@
         <v>30</v>
       </c>
       <c r="F11" s="9" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="I11" s="11" t="s">
         <v>9</v>
@@ -1413,7 +1952,7 @@
       <c r="F12" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="I12" s="42" t="s">
+      <c r="I12" s="36" t="s">
         <v>16</v>
       </c>
       <c r="J12" s="9" t="s">
@@ -1457,14 +1996,14 @@
         <v>68</v>
       </c>
       <c r="H14" s="6"/>
-      <c r="I14" s="31" t="s">
-        <v>92</v>
-      </c>
-      <c r="J14" s="30" t="s">
-        <v>93</v>
+      <c r="I14" s="29" t="s">
+        <v>84</v>
+      </c>
+      <c r="J14" s="28" t="s">
+        <v>85</v>
       </c>
       <c r="K14" s="5" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.3">
@@ -1473,10 +2012,10 @@
         <v>40</v>
       </c>
       <c r="C15" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="D15" s="16" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="E15">
         <v>30</v>
@@ -1486,10 +2025,10 @@
       </c>
       <c r="H15" s="6"/>
       <c r="J15" s="15" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="K15" s="8" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.3">
@@ -1510,16 +2049,16 @@
         <v>70</v>
       </c>
       <c r="J16" s="15" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="K16" s="8" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A17" s="23"/>
       <c r="B17" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="C17" t="s">
         <v>56</v>
@@ -1531,13 +2070,13 @@
         <v>24</v>
       </c>
       <c r="F17" s="8" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="J17" s="15" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="K17" s="8" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.3">
@@ -1558,10 +2097,10 @@
         <v>71</v>
       </c>
       <c r="J18" s="15" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="K18" s="8" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.3">
@@ -1581,13 +2120,13 @@
       <c r="F19" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="H19" s="37" t="s">
-        <v>115</v>
-      </c>
-      <c r="I19" s="38" t="s">
-        <v>114</v>
-      </c>
-      <c r="J19" s="40"/>
+      <c r="H19" s="33" t="s">
+        <v>107</v>
+      </c>
+      <c r="I19" s="34" t="s">
+        <v>106</v>
+      </c>
+      <c r="J19" s="28"/>
       <c r="K19" s="13"/>
       <c r="L19" s="13"/>
       <c r="M19" s="13"/>
@@ -1613,10 +2152,10 @@
       <c r="F20" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="I20" s="39" t="s">
-        <v>116</v>
-      </c>
-      <c r="J20" s="41"/>
+      <c r="I20" s="35" t="s">
+        <v>108</v>
+      </c>
+      <c r="J20" s="17"/>
       <c r="K20" s="7"/>
       <c r="L20" s="7"/>
       <c r="M20" s="7"/>
@@ -1659,13 +2198,13 @@
         <v>80</v>
       </c>
       <c r="I22" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="J22" s="12" t="s">
-        <v>104</v>
-      </c>
-      <c r="K22" s="32" t="s">
-        <v>105</v>
+        <v>96</v>
+      </c>
+      <c r="K22" s="30" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.3">
@@ -1685,30 +2224,35 @@
       <c r="F23" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="J23" s="30" t="s">
+      <c r="J23" s="28" t="s">
         <v>19</v>
       </c>
       <c r="K23" s="5" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.3">
       <c r="J24" s="15" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="K24" s="8" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
-        <v>124</v>
-      </c>
+        <v>103</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15" ht="26.25" x14ac:dyDescent="0.45">
+      <c r="A25" s="44"/>
+      <c r="B25" s="44"/>
+      <c r="C25" s="44"/>
+      <c r="D25" s="44" t="s">
+        <v>116</v>
+      </c>
+      <c r="E25" s="44"/>
+      <c r="F25" s="44"/>
       <c r="J25" s="15" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="K25" s="8" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.3">
@@ -1731,10 +2275,10 @@
         <v>73</v>
       </c>
       <c r="J26" s="15" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="K26" s="8" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.3">
@@ -1755,10 +2299,10 @@
         <v>74</v>
       </c>
       <c r="J27" s="15" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="K27" s="8" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.3">
@@ -1779,10 +2323,10 @@
         <v>75</v>
       </c>
       <c r="J28" s="15" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="K28" s="8" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.3">
@@ -1806,11 +2350,11 @@
         <v>22</v>
       </c>
       <c r="K29" s="9" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A30" s="35" t="s">
+      <c r="A30" s="31" t="s">
         <v>49</v>
       </c>
       <c r="B30" s="2" t="s">
@@ -1819,7 +2363,7 @@
       <c r="C30" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="D30" s="36">
+      <c r="D30" s="32">
         <v>4</v>
       </c>
       <c r="E30" s="2">
@@ -1828,6 +2372,12 @@
       <c r="F30" s="3" t="s">
         <v>79</v>
       </c>
+    </row>
+    <row r="35" spans="4:5" ht="31.5" x14ac:dyDescent="0.55000000000000004">
+      <c r="D35" s="77" t="s">
+        <v>190</v>
+      </c>
+      <c r="E35" s="78"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -1836,68 +2386,1449 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D90419A6-6419-4C59-83BA-ADE2E060AC43}">
-  <dimension ref="A1:E6"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E983E940-0B95-4E42-9EE1-D16687E05FB1}">
+  <dimension ref="A1:O47"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.375" customWidth="1"/>
-    <col min="2" max="2" width="14.375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.75" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="26.375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="30" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.25" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="24.5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.25" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="17.875" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="11" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="28.375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="17.625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="43.25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+    <row r="1" spans="1:15" ht="26.25" x14ac:dyDescent="0.45">
+      <c r="A1" s="76"/>
+      <c r="B1" s="76"/>
+      <c r="C1" s="76"/>
+      <c r="D1" s="76"/>
+      <c r="E1" s="76" t="s">
+        <v>185</v>
+      </c>
+      <c r="F1" s="76"/>
+      <c r="G1" s="76"/>
+      <c r="H1" s="76"/>
+      <c r="I1" s="76"/>
+    </row>
+    <row r="2" spans="1:15" ht="26.25" x14ac:dyDescent="0.5">
+      <c r="A2" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B2" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="20" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="20" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="F2" s="21" t="s">
+        <v>5</v>
+      </c>
+      <c r="G2" s="21" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" s="25" t="s">
+      <c r="H2" s="21" t="s">
+        <v>125</v>
+      </c>
+      <c r="I2" s="21" t="s">
+        <v>128</v>
+      </c>
+      <c r="L2" s="39"/>
+      <c r="M2" s="39" t="s">
+        <v>133</v>
+      </c>
+      <c r="N2" s="40"/>
+      <c r="O2" s="40"/>
+    </row>
+    <row r="3" spans="1:15" ht="20.25" x14ac:dyDescent="0.35">
+      <c r="A3" s="22" t="s">
+        <v>26</v>
+      </c>
+      <c r="B3" s="13" t="s">
+        <v>193</v>
+      </c>
+      <c r="C3" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="D3" s="13">
         <v>2</v>
       </c>
-      <c r="B2" s="28" t="s">
-        <v>83</v>
-      </c>
-      <c r="D2" s="29" t="s">
-        <v>89</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" s="15" t="s">
+      <c r="E3" s="13">
+        <v>36</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="G3" s="34">
+        <v>1200</v>
+      </c>
+      <c r="H3" s="34">
+        <f>G3*E3</f>
+        <v>43200</v>
+      </c>
+      <c r="I3" s="5">
+        <f>H3/10000</f>
+        <v>4.32</v>
+      </c>
+      <c r="L3" s="53"/>
+      <c r="M3" s="54" t="s">
+        <v>118</v>
+      </c>
+      <c r="N3" s="54" t="s">
+        <v>119</v>
+      </c>
+      <c r="O3" s="55" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" ht="20.25" x14ac:dyDescent="0.35">
+      <c r="A4" s="23"/>
+      <c r="B4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C4" t="s">
+        <v>113</v>
+      </c>
+      <c r="D4" s="16" t="s">
+        <v>206</v>
+      </c>
+      <c r="E4">
+        <v>30</v>
+      </c>
+      <c r="F4" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="G4" s="45">
+        <v>1856</v>
+      </c>
+      <c r="H4" s="45">
+        <f>G4*E4</f>
+        <v>55680</v>
+      </c>
+      <c r="I4" s="8">
+        <f>H4/10000</f>
+        <v>5.5679999999999996</v>
+      </c>
+      <c r="K4" s="64" t="s">
+        <v>26</v>
+      </c>
+      <c r="L4" s="56" t="s">
+        <v>123</v>
+      </c>
+      <c r="M4" s="57" t="s">
+        <v>117</v>
+      </c>
+      <c r="N4" s="57" t="s">
+        <v>120</v>
+      </c>
+      <c r="O4" s="58" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" ht="20.25" x14ac:dyDescent="0.35">
+      <c r="A5" s="23"/>
+      <c r="B5" t="s">
+        <v>29</v>
+      </c>
+      <c r="C5" t="s">
+        <v>113</v>
+      </c>
+      <c r="D5" s="16" t="s">
+        <v>206</v>
+      </c>
+      <c r="E5">
+        <v>28</v>
+      </c>
+      <c r="F5" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="G5" s="45">
+        <v>2010</v>
+      </c>
+      <c r="H5" s="45">
+        <f t="shared" ref="H5:H11" si="0">G5*E5</f>
+        <v>56280</v>
+      </c>
+      <c r="I5" s="8">
+        <f t="shared" ref="I5:I11" si="1">H5/10000</f>
+        <v>5.6280000000000001</v>
+      </c>
+      <c r="L5" s="56" t="s">
+        <v>124</v>
+      </c>
+      <c r="M5" s="59">
+        <v>315</v>
+      </c>
+      <c r="N5" s="59">
+        <v>460</v>
+      </c>
+      <c r="O5" s="60">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" ht="20.25" x14ac:dyDescent="0.35">
+      <c r="A6" s="23"/>
+      <c r="B6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C6" t="s">
+        <v>56</v>
+      </c>
+      <c r="D6" s="16">
+        <v>2</v>
+      </c>
+      <c r="E6">
+        <v>18</v>
+      </c>
+      <c r="F6" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="G6" s="45">
+        <v>920</v>
+      </c>
+      <c r="H6" s="45">
+        <f t="shared" si="0"/>
+        <v>16560</v>
+      </c>
+      <c r="I6" s="8">
+        <f t="shared" si="1"/>
+        <v>1.6559999999999999</v>
+      </c>
+      <c r="K6" s="64" t="s">
+        <v>126</v>
+      </c>
+      <c r="L6" s="56" t="s">
+        <v>123</v>
+      </c>
+      <c r="M6" s="57">
+        <f t="shared" ref="M6:N6" si="2">M7*12</f>
+        <v>4560</v>
+      </c>
+      <c r="N6" s="57">
+        <f t="shared" si="2"/>
+        <v>7800</v>
+      </c>
+      <c r="O6" s="58">
+        <f>O7*12</f>
+        <v>10200</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" ht="20.25" x14ac:dyDescent="0.35">
+      <c r="A7" s="24"/>
+      <c r="B7" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="D7" s="18">
+        <v>3</v>
+      </c>
+      <c r="E7" s="7">
+        <v>18</v>
+      </c>
+      <c r="F7" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="G7" s="45">
+        <v>1380</v>
+      </c>
+      <c r="H7" s="45">
+        <f t="shared" si="0"/>
+        <v>24840</v>
+      </c>
+      <c r="I7" s="8">
+        <f t="shared" si="1"/>
+        <v>2.484</v>
+      </c>
+      <c r="L7" s="56" t="s">
+        <v>124</v>
+      </c>
+      <c r="M7" s="59">
+        <v>380</v>
+      </c>
+      <c r="N7" s="59">
+        <v>650</v>
+      </c>
+      <c r="O7" s="60">
+        <v>850</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" ht="20.25" x14ac:dyDescent="0.35">
+      <c r="A8" s="25" t="s">
+        <v>32</v>
+      </c>
+      <c r="B8" s="13" t="s">
+        <v>194</v>
+      </c>
+      <c r="C8" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="D8" s="19">
+        <v>2</v>
+      </c>
+      <c r="E8" s="13">
+        <v>36</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="G8" s="45">
+        <v>1700</v>
+      </c>
+      <c r="H8" s="45">
+        <f t="shared" si="0"/>
+        <v>61200</v>
+      </c>
+      <c r="I8" s="8">
+        <f t="shared" si="1"/>
+        <v>6.12</v>
+      </c>
+      <c r="K8" s="64" t="s">
+        <v>36</v>
+      </c>
+      <c r="L8" s="56" t="s">
+        <v>123</v>
+      </c>
+      <c r="M8" s="57">
+        <f t="shared" ref="M8:N8" si="3">M9*12</f>
+        <v>3840</v>
+      </c>
+      <c r="N8" s="57">
+        <f t="shared" si="3"/>
+        <v>5760</v>
+      </c>
+      <c r="O8" s="58">
+        <f>O9*12</f>
+        <v>8400</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" ht="20.25" x14ac:dyDescent="0.35">
+      <c r="A9" s="26"/>
+      <c r="B9" t="s">
+        <v>34</v>
+      </c>
+      <c r="C9" t="s">
+        <v>56</v>
+      </c>
+      <c r="D9" s="16">
+        <v>5</v>
+      </c>
+      <c r="E9">
+        <v>30</v>
+      </c>
+      <c r="F9" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="G9" s="45">
+        <v>3250</v>
+      </c>
+      <c r="H9" s="45">
+        <f t="shared" si="0"/>
+        <v>97500</v>
+      </c>
+      <c r="I9" s="8">
+        <f t="shared" si="1"/>
+        <v>9.75</v>
+      </c>
+      <c r="L9" s="56" t="s">
+        <v>124</v>
+      </c>
+      <c r="M9" s="59">
+        <v>320</v>
+      </c>
+      <c r="N9" s="59">
+        <v>480</v>
+      </c>
+      <c r="O9" s="60">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" ht="20.25" x14ac:dyDescent="0.35">
+      <c r="A10" s="26"/>
+      <c r="B10" t="s">
+        <v>35</v>
+      </c>
+      <c r="C10" t="s">
+        <v>55</v>
+      </c>
+      <c r="D10" s="16">
+        <v>2</v>
+      </c>
+      <c r="E10">
+        <v>30</v>
+      </c>
+      <c r="F10" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="G10" s="45">
+        <v>1700</v>
+      </c>
+      <c r="H10" s="45">
+        <f t="shared" si="0"/>
+        <v>51000</v>
+      </c>
+      <c r="I10" s="8">
+        <f t="shared" si="1"/>
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="K10" s="64" t="s">
+        <v>127</v>
+      </c>
+      <c r="L10" s="56" t="s">
+        <v>123</v>
+      </c>
+      <c r="M10" s="57">
+        <f t="shared" ref="M10:N10" si="4">M11*12</f>
+        <v>3000</v>
+      </c>
+      <c r="N10" s="57">
+        <f t="shared" si="4"/>
+        <v>5040</v>
+      </c>
+      <c r="O10" s="58">
+        <f>O11*12</f>
+        <v>8400</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" ht="20.25" x14ac:dyDescent="0.35">
+      <c r="A11" s="26"/>
+      <c r="B11" t="s">
+        <v>111</v>
+      </c>
+      <c r="C11" t="s">
+        <v>56</v>
+      </c>
+      <c r="D11" s="16">
+        <v>2</v>
+      </c>
+      <c r="E11">
+        <v>30</v>
+      </c>
+      <c r="F11" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="G11" s="45">
+        <v>1300</v>
+      </c>
+      <c r="H11" s="45">
+        <f t="shared" si="0"/>
+        <v>39000</v>
+      </c>
+      <c r="I11" s="8">
+        <f t="shared" si="1"/>
+        <v>3.9</v>
+      </c>
+      <c r="L11" s="56" t="s">
+        <v>124</v>
+      </c>
+      <c r="M11" s="59">
+        <v>250</v>
+      </c>
+      <c r="N11" s="59">
+        <v>420</v>
+      </c>
+      <c r="O11" s="60">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" ht="20.25" x14ac:dyDescent="0.35">
+      <c r="A12" s="79"/>
+      <c r="B12" t="s">
+        <v>205</v>
+      </c>
+      <c r="C12" t="s">
+        <v>56</v>
+      </c>
+      <c r="D12" s="16">
+        <v>4</v>
+      </c>
+      <c r="E12">
+        <v>30</v>
+      </c>
+      <c r="F12" t="s">
+        <v>195</v>
+      </c>
+      <c r="G12" s="45">
+        <v>2600</v>
+      </c>
+      <c r="H12" s="45">
+        <f t="shared" ref="H12" si="5">G12*E12</f>
+        <v>78000</v>
+      </c>
+      <c r="I12" s="8">
+        <f t="shared" ref="I12" si="6">H12/10000</f>
+        <v>7.8</v>
+      </c>
+      <c r="K12" s="64" t="s">
+        <v>116</v>
+      </c>
+      <c r="L12" s="56" t="s">
+        <v>123</v>
+      </c>
+      <c r="M12" s="57"/>
+      <c r="N12" s="57">
+        <f>N13*12</f>
+        <v>6000</v>
+      </c>
+      <c r="O12" s="58">
+        <f>O13*12</f>
+        <v>9600</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" ht="20.25" x14ac:dyDescent="0.35">
+      <c r="A13" s="79"/>
+      <c r="B13" t="s">
+        <v>197</v>
+      </c>
+      <c r="C13" t="s">
+        <v>198</v>
+      </c>
+      <c r="D13" s="16" t="s">
+        <v>115</v>
+      </c>
+      <c r="E13">
+        <v>30</v>
+      </c>
+      <c r="F13" t="s">
+        <v>209</v>
+      </c>
+      <c r="G13" s="45">
+        <v>2150</v>
+      </c>
+      <c r="H13" s="45">
+        <f t="shared" ref="H13" si="7">G13*E13</f>
+        <v>64500</v>
+      </c>
+      <c r="I13" s="8">
+        <f t="shared" ref="I13" si="8">H13/10000</f>
+        <v>6.45</v>
+      </c>
+      <c r="L13" s="61" t="s">
+        <v>124</v>
+      </c>
+      <c r="M13" s="62"/>
+      <c r="N13" s="62">
+        <v>500</v>
+      </c>
+      <c r="O13" s="63">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A14" s="79"/>
+      <c r="B14" t="s">
+        <v>207</v>
+      </c>
+      <c r="C14" t="s">
+        <v>198</v>
+      </c>
+      <c r="D14" s="16" t="s">
+        <v>115</v>
+      </c>
+      <c r="E14">
+        <v>30</v>
+      </c>
+      <c r="F14" t="s">
+        <v>208</v>
+      </c>
+      <c r="G14" s="45">
+        <v>2150</v>
+      </c>
+      <c r="H14" s="45">
+        <f t="shared" ref="H14:H26" si="9">G14*E14</f>
+        <v>64500</v>
+      </c>
+      <c r="I14" s="8">
+        <f t="shared" ref="I14:I26" si="10">H14/10000</f>
+        <v>6.45</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" ht="26.25" x14ac:dyDescent="0.5">
+      <c r="A15" s="22" t="s">
+        <v>36</v>
+      </c>
+      <c r="B15" s="13" t="s">
+        <v>196</v>
+      </c>
+      <c r="C15" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="D15" s="19">
+        <v>1</v>
+      </c>
+      <c r="E15" s="13">
+        <v>36</v>
+      </c>
+      <c r="F15" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="G15" s="45">
+        <v>700</v>
+      </c>
+      <c r="H15" s="45">
+        <f t="shared" si="9"/>
+        <v>25200</v>
+      </c>
+      <c r="I15" s="8">
+        <f t="shared" si="10"/>
+        <v>2.52</v>
+      </c>
+      <c r="L15" s="37"/>
+      <c r="M15" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="N15" s="37"/>
+      <c r="O15" s="37"/>
+    </row>
+    <row r="16" spans="1:15" ht="20.25" x14ac:dyDescent="0.35">
+      <c r="A16" s="23"/>
+      <c r="B16" t="s">
+        <v>38</v>
+      </c>
+      <c r="C16" t="s">
+        <v>56</v>
+      </c>
+      <c r="D16" s="16">
+        <v>1</v>
+      </c>
+      <c r="E16">
+        <v>25</v>
+      </c>
+      <c r="F16" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="G16" s="45">
+        <v>480</v>
+      </c>
+      <c r="H16" s="45">
+        <f t="shared" si="9"/>
+        <v>12000</v>
+      </c>
+      <c r="I16" s="8">
+        <f t="shared" si="10"/>
+        <v>1.2</v>
+      </c>
+      <c r="L16" s="68" t="s">
+        <v>144</v>
+      </c>
+      <c r="M16" s="13" t="s">
+        <v>145</v>
+      </c>
+      <c r="N16" s="13" t="s">
+        <v>146</v>
+      </c>
+      <c r="O16" s="5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" ht="20.25" x14ac:dyDescent="0.35">
+      <c r="A17" s="23"/>
+      <c r="B17" t="s">
+        <v>39</v>
+      </c>
+      <c r="C17" t="s">
+        <v>56</v>
+      </c>
+      <c r="D17" s="16">
+        <v>1</v>
+      </c>
+      <c r="E17">
+        <v>30</v>
+      </c>
+      <c r="F17" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="G17" s="45">
+        <v>480</v>
+      </c>
+      <c r="H17" s="45">
+        <f t="shared" si="9"/>
+        <v>14400</v>
+      </c>
+      <c r="I17" s="8">
+        <f t="shared" si="10"/>
+        <v>1.44</v>
+      </c>
+      <c r="K17" s="46" t="s">
+        <v>135</v>
+      </c>
+      <c r="L17" s="56" t="s">
+        <v>136</v>
+      </c>
+      <c r="M17" t="s">
+        <v>147</v>
+      </c>
+      <c r="N17" t="s">
+        <v>153</v>
+      </c>
+      <c r="O17" s="8" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" ht="20.25" x14ac:dyDescent="0.35">
+      <c r="A18" s="23"/>
+      <c r="B18" t="s">
+        <v>40</v>
+      </c>
+      <c r="C18" t="s">
+        <v>113</v>
+      </c>
+      <c r="D18" s="16">
+        <v>2</v>
+      </c>
+      <c r="E18">
+        <v>30</v>
+      </c>
+      <c r="F18" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="G18" s="45">
+        <v>800</v>
+      </c>
+      <c r="H18" s="45">
+        <f t="shared" si="9"/>
+        <v>24000</v>
+      </c>
+      <c r="I18" s="8">
+        <f t="shared" si="10"/>
+        <v>2.4</v>
+      </c>
+      <c r="L18" s="56" t="s">
+        <v>137</v>
+      </c>
+      <c r="M18" t="s">
+        <v>147</v>
+      </c>
+      <c r="N18" t="s">
+        <v>152</v>
+      </c>
+      <c r="O18" s="8" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" ht="20.25" x14ac:dyDescent="0.35">
+      <c r="A19" s="23"/>
+      <c r="B19" t="s">
+        <v>41</v>
+      </c>
+      <c r="C19" t="s">
+        <v>56</v>
+      </c>
+      <c r="D19" s="16">
+        <v>2</v>
+      </c>
+      <c r="E19">
+        <v>28</v>
+      </c>
+      <c r="F19" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="G19" s="45">
+        <v>960</v>
+      </c>
+      <c r="H19" s="45">
+        <f t="shared" si="9"/>
+        <v>26880</v>
+      </c>
+      <c r="I19" s="8">
+        <f t="shared" si="10"/>
+        <v>2.6880000000000002</v>
+      </c>
+      <c r="L19" s="56" t="s">
+        <v>138</v>
+      </c>
+      <c r="M19" t="s">
+        <v>147</v>
+      </c>
+      <c r="N19" t="s">
+        <v>151</v>
+      </c>
+      <c r="O19" s="8" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" ht="20.25" x14ac:dyDescent="0.35">
+      <c r="A20" s="23"/>
+      <c r="B20" t="s">
+        <v>109</v>
+      </c>
+      <c r="C20" t="s">
+        <v>56</v>
+      </c>
+      <c r="D20" s="16">
+        <v>1</v>
+      </c>
+      <c r="E20">
+        <v>24</v>
+      </c>
+      <c r="F20" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="G20" s="45">
+        <v>480</v>
+      </c>
+      <c r="H20" s="45">
+        <f t="shared" si="9"/>
+        <v>11520</v>
+      </c>
+      <c r="I20" s="8">
+        <f t="shared" si="10"/>
+        <v>1.1519999999999999</v>
+      </c>
+      <c r="K20" s="46" t="s">
+        <v>143</v>
+      </c>
+      <c r="L20" s="56" t="s">
+        <v>139</v>
+      </c>
+      <c r="M20" t="s">
+        <v>148</v>
+      </c>
+      <c r="N20" t="s">
+        <v>187</v>
+      </c>
+      <c r="O20" s="8" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" ht="20.25" x14ac:dyDescent="0.35">
+      <c r="A21" s="23"/>
+      <c r="B21" t="s">
+        <v>42</v>
+      </c>
+      <c r="C21" t="s">
+        <v>56</v>
+      </c>
+      <c r="D21" s="16">
+        <v>2</v>
+      </c>
+      <c r="E21">
+        <v>24</v>
+      </c>
+      <c r="F21" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="G21" s="45">
+        <v>960</v>
+      </c>
+      <c r="H21" s="45">
+        <f t="shared" si="9"/>
+        <v>23040</v>
+      </c>
+      <c r="I21" s="8">
+        <f t="shared" si="10"/>
+        <v>2.3039999999999998</v>
+      </c>
+      <c r="K21" s="46" t="s">
+        <v>142</v>
+      </c>
+      <c r="L21" s="56" t="s">
+        <v>140</v>
+      </c>
+      <c r="M21" t="s">
+        <v>149</v>
+      </c>
+      <c r="N21" t="s">
+        <v>188</v>
+      </c>
+      <c r="O21" s="8" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" ht="20.25" x14ac:dyDescent="0.35">
+      <c r="A22" s="24"/>
+      <c r="B22" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="C22" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="D22" s="18">
+        <v>1</v>
+      </c>
+      <c r="E22" s="7">
+        <v>20</v>
+      </c>
+      <c r="F22" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="G22" s="45">
+        <v>480</v>
+      </c>
+      <c r="H22" s="45">
+        <f t="shared" si="9"/>
+        <v>9600</v>
+      </c>
+      <c r="I22" s="8">
+        <f t="shared" si="10"/>
+        <v>0.96</v>
+      </c>
+      <c r="L22" s="56" t="s">
+        <v>141</v>
+      </c>
+      <c r="M22" t="s">
+        <v>149</v>
+      </c>
+      <c r="N22" t="s">
+        <v>150</v>
+      </c>
+      <c r="O22" s="8" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A23" s="22" t="s">
+        <v>49</v>
+      </c>
+      <c r="B23" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="C23" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="D23" s="19">
+        <v>1</v>
+      </c>
+      <c r="E23" s="13">
+        <v>36</v>
+      </c>
+      <c r="F23" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="G23" s="45">
+        <v>700</v>
+      </c>
+      <c r="H23" s="45">
+        <f t="shared" si="9"/>
+        <v>25200</v>
+      </c>
+      <c r="I23" s="8">
+        <f t="shared" si="10"/>
+        <v>2.52</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A24" s="23"/>
+      <c r="B24" t="s">
+        <v>51</v>
+      </c>
+      <c r="C24" t="s">
+        <v>56</v>
+      </c>
+      <c r="D24" s="16">
+        <v>1</v>
+      </c>
+      <c r="E24">
+        <v>18</v>
+      </c>
+      <c r="F24" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="G24" s="45">
+        <v>420</v>
+      </c>
+      <c r="H24" s="45">
+        <f t="shared" si="9"/>
+        <v>7560</v>
+      </c>
+      <c r="I24" s="8">
+        <f t="shared" si="10"/>
+        <v>0.75600000000000001</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A25" s="23"/>
+      <c r="B25" t="s">
+        <v>53</v>
+      </c>
+      <c r="C25" t="s">
+        <v>56</v>
+      </c>
+      <c r="D25" s="16">
+        <v>1</v>
+      </c>
+      <c r="E25">
+        <v>24</v>
+      </c>
+      <c r="F25" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="G25" s="45">
+        <v>420</v>
+      </c>
+      <c r="H25" s="45">
+        <f t="shared" si="9"/>
+        <v>10080</v>
+      </c>
+      <c r="I25" s="8">
+        <f t="shared" si="10"/>
+        <v>1.008</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A26" s="24"/>
+      <c r="B26" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="C26" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="B3" s="8" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" s="15" t="s">
+      <c r="D26" s="18">
+        <v>1</v>
+      </c>
+      <c r="E26" s="7">
+        <v>6</v>
+      </c>
+      <c r="F26" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="G26" s="35">
+        <v>250</v>
+      </c>
+      <c r="H26" s="35">
+        <f t="shared" si="9"/>
+        <v>1500</v>
+      </c>
+      <c r="I26" s="9">
+        <f t="shared" si="10"/>
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="F27" s="47" t="s">
+        <v>177</v>
+      </c>
+      <c r="G27" s="48">
+        <f t="shared" ref="G27:H27" si="11">SUM(G6:G26)</f>
+        <v>24280</v>
+      </c>
+      <c r="H27" s="48">
+        <f t="shared" si="11"/>
+        <v>688080</v>
+      </c>
+      <c r="I27" s="49">
+        <f>SUM(I3:I26)</f>
+        <v>84.323999999999998</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15" ht="20.25" x14ac:dyDescent="0.35">
+      <c r="A28" s="41"/>
+      <c r="B28" s="42"/>
+      <c r="C28" s="41" t="s">
+        <v>116</v>
+      </c>
+      <c r="D28" s="42"/>
+      <c r="E28" s="42"/>
+      <c r="F28" s="42"/>
+      <c r="G28" s="42" t="s">
+        <v>172</v>
+      </c>
+      <c r="H28" s="42" t="s">
+        <v>161</v>
+      </c>
+      <c r="I28" s="42" t="s">
+        <v>178</v>
+      </c>
+      <c r="K28" s="80" t="s">
+        <v>191</v>
+      </c>
+      <c r="L28" s="90" t="s">
+        <v>201</v>
+      </c>
+      <c r="M28" s="91"/>
+      <c r="N28" s="91" t="s">
+        <v>202</v>
+      </c>
+      <c r="O28" s="92"/>
+    </row>
+    <row r="29" spans="1:15" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="A29" s="25" t="s">
+        <v>44</v>
+      </c>
+      <c r="B29" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="C29" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="D29" s="19">
+        <v>1</v>
+      </c>
+      <c r="E29" s="13">
+        <v>14</v>
+      </c>
+      <c r="F29" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="G29" s="5">
+        <v>720</v>
+      </c>
+      <c r="H29" s="13">
+        <v>14</v>
+      </c>
+      <c r="I29" s="34">
+        <f>(G29*H29)</f>
+        <v>10080</v>
+      </c>
+      <c r="K29" s="81"/>
+      <c r="L29" s="88" t="s">
+        <v>192</v>
+      </c>
+      <c r="M29" s="89"/>
+      <c r="N29" s="93" t="s">
+        <v>203</v>
+      </c>
+      <c r="O29" s="94"/>
+    </row>
+    <row r="30" spans="1:15" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="A30" s="26"/>
+      <c r="B30" t="s">
+        <v>46</v>
+      </c>
+      <c r="C30" t="s">
         <v>56</v>
       </c>
-      <c r="B4" s="8" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" s="15" t="s">
+      <c r="D30" s="16">
+        <v>1</v>
+      </c>
+      <c r="E30">
+        <v>7</v>
+      </c>
+      <c r="F30" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="G30" s="8">
+        <v>200</v>
+      </c>
+      <c r="H30">
+        <v>25</v>
+      </c>
+      <c r="I30" s="45">
+        <f t="shared" ref="I30:I31" si="12">(G30*H30)</f>
+        <v>5000</v>
+      </c>
+      <c r="K30" s="81"/>
+      <c r="L30" s="84" t="s">
+        <v>200</v>
+      </c>
+      <c r="M30" s="85"/>
+      <c r="N30" s="95" t="s">
+        <v>204</v>
+      </c>
+      <c r="O30" s="96"/>
+    </row>
+    <row r="31" spans="1:15" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="A31" s="26"/>
+      <c r="B31" t="s">
+        <v>47</v>
+      </c>
+      <c r="C31" t="s">
+        <v>56</v>
+      </c>
+      <c r="D31" s="16">
+        <v>1</v>
+      </c>
+      <c r="E31">
+        <v>18</v>
+      </c>
+      <c r="F31" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="G31" s="8">
+        <v>10</v>
+      </c>
+      <c r="H31">
+        <v>550</v>
+      </c>
+      <c r="I31" s="45">
+        <f t="shared" si="12"/>
+        <v>5500</v>
+      </c>
+      <c r="K31" s="81"/>
+      <c r="L31" s="84"/>
+      <c r="M31" s="85"/>
+      <c r="N31" s="95" t="s">
+        <v>210</v>
+      </c>
+      <c r="O31" s="96"/>
+    </row>
+    <row r="32" spans="1:15" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="A32" s="27"/>
+      <c r="B32" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="C32" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="B5" s="8" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" s="17" t="s">
-        <v>84</v>
-      </c>
-      <c r="B6" s="9" t="s">
-        <v>88</v>
+      <c r="D32" s="18">
+        <v>10</v>
+      </c>
+      <c r="E32" s="7">
+        <v>4</v>
+      </c>
+      <c r="F32" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="G32" s="9">
+        <v>1500</v>
+      </c>
+      <c r="H32" s="7">
+        <v>10</v>
+      </c>
+      <c r="I32" s="35">
+        <f>(G32*H32)</f>
+        <v>15000</v>
+      </c>
+      <c r="K32" s="81"/>
+      <c r="L32" s="86"/>
+      <c r="M32" s="87"/>
+      <c r="N32" s="82" t="s">
+        <v>211</v>
+      </c>
+      <c r="O32" s="83"/>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A33" s="31" t="s">
+        <v>49</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D33" s="32">
+        <v>4</v>
+      </c>
+      <c r="E33" s="2">
+        <v>12</v>
+      </c>
+      <c r="F33" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="G33" s="3">
+        <v>250</v>
+      </c>
+      <c r="H33" s="65" t="s">
+        <v>162</v>
+      </c>
+      <c r="I33" s="9">
+        <v>12000</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="H34" s="47" t="s">
+        <v>177</v>
+      </c>
+      <c r="I34" s="3">
+        <f>(SUM(I29:I33)/10000)</f>
+        <v>4.758</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" ht="20.25" x14ac:dyDescent="0.35">
+      <c r="A35" s="43"/>
+      <c r="B35" s="43"/>
+      <c r="C35" s="43" t="s">
+        <v>129</v>
+      </c>
+      <c r="D35" s="43"/>
+      <c r="E35" s="43"/>
+      <c r="F35" s="43"/>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A36" s="50"/>
+      <c r="B36" s="51" t="s">
+        <v>164</v>
+      </c>
+      <c r="C36" s="51" t="s">
+        <v>165</v>
+      </c>
+      <c r="D36" s="51" t="s">
+        <v>172</v>
+      </c>
+      <c r="E36" s="51" t="s">
+        <v>168</v>
+      </c>
+      <c r="F36" s="52" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A37" s="26" t="s">
+        <v>131</v>
+      </c>
+      <c r="B37" t="s">
+        <v>166</v>
+      </c>
+      <c r="C37" t="s">
+        <v>167</v>
+      </c>
+      <c r="D37">
+        <v>15</v>
+      </c>
+      <c r="E37">
+        <v>1.78</v>
+      </c>
+      <c r="F37" s="8" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A38" s="26" t="s">
+        <v>132</v>
+      </c>
+      <c r="B38" t="s">
+        <v>170</v>
+      </c>
+      <c r="C38" t="s">
+        <v>167</v>
+      </c>
+      <c r="D38">
+        <v>300</v>
+      </c>
+      <c r="E38">
+        <v>1.8</v>
+      </c>
+      <c r="F38" s="8" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A39" s="26" t="s">
+        <v>163</v>
+      </c>
+      <c r="B39" t="s">
+        <v>171</v>
+      </c>
+      <c r="C39" t="s">
+        <v>173</v>
+      </c>
+      <c r="D39">
+        <v>500</v>
+      </c>
+      <c r="E39">
+        <v>0.2</v>
+      </c>
+      <c r="F39" s="8" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A40" s="27" t="s">
+        <v>130</v>
+      </c>
+      <c r="B40" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="C40" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="D40" s="66">
+        <v>12000</v>
+      </c>
+      <c r="E40" s="7">
+        <v>1.2</v>
+      </c>
+      <c r="F40" s="9" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="D41" s="67" t="s">
+        <v>177</v>
+      </c>
+      <c r="E41" s="3">
+        <f>SUM(E37:E40)</f>
+        <v>4.9800000000000004</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" ht="20.25" x14ac:dyDescent="0.35">
+      <c r="A42" s="43"/>
+      <c r="B42" s="43"/>
+      <c r="C42" s="43" t="s">
+        <v>186</v>
+      </c>
+      <c r="D42" s="43"/>
+      <c r="E42" s="43"/>
+      <c r="F42" s="43"/>
+      <c r="G42" s="43"/>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A43" s="50"/>
+      <c r="B43" s="73" t="s">
+        <v>180</v>
+      </c>
+      <c r="C43" s="73" t="s">
+        <v>160</v>
+      </c>
+      <c r="D43" s="73" t="s">
+        <v>184</v>
+      </c>
+      <c r="E43" s="51" t="s">
+        <v>5</v>
+      </c>
+      <c r="F43" s="51"/>
+      <c r="G43" s="52"/>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A44" s="27" t="s">
+        <v>179</v>
+      </c>
+      <c r="B44" s="74" t="s">
+        <v>181</v>
+      </c>
+      <c r="C44" s="75" t="s">
+        <v>182</v>
+      </c>
+      <c r="D44" s="74">
+        <v>3</v>
+      </c>
+      <c r="E44" s="71" t="s">
+        <v>183</v>
+      </c>
+      <c r="F44" s="71"/>
+      <c r="G44" s="72"/>
+    </row>
+    <row r="46" spans="1:10" ht="26.25" x14ac:dyDescent="0.45">
+      <c r="A46" s="69" t="s">
+        <v>189</v>
+      </c>
+      <c r="B46" s="70">
+        <f>SUM(E41,I34,I27,D44)</f>
+        <v>97.061999999999998</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="J47" t="s">
+        <v>199</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="N32:O32"/>
+    <mergeCell ref="L30:M32"/>
+    <mergeCell ref="L29:M29"/>
+    <mergeCell ref="L28:M28"/>
+    <mergeCell ref="N28:O28"/>
+    <mergeCell ref="N29:O29"/>
+    <mergeCell ref="N30:O30"/>
+    <mergeCell ref="N31:O31"/>
+  </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
